--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1869,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1879,6 +1879,20 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1750,6 +1750,42 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>chestpressflat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>plank</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>legraise</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>oblique</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1893,6 +1929,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,6 +1786,150 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>oblique</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>shoulderpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ropepushdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>benchdips</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>latpulldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>curls</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>plank</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>legraise</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>oblique</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>stretching</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
         </is>
       </c>
     </row>
@@ -1905,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1936,6 +2080,20 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1930,6 +1930,54 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>shoulderpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ropepushdown</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2094,6 +2142,48 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1978,6 +1978,54 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>ropepushdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>latpulldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>curls</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>affondi</t>
         </is>
       </c>
     </row>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2026,6 +2026,138 @@
       <c r="B37" t="inlineStr">
         <is>
           <t>affondi</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>stretching</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>plank</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>legraise</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>oblique</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ropepushdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>shoulderpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>affondi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>latpulldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>curls</t>
         </is>
       </c>
     </row>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,6 +2158,138 @@
       <c r="B48" t="inlineStr">
         <is>
           <t>curls</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>plank</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>legraise</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>oblique</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>stretching</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ropepushdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>shoulderpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>latpulldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>curls</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>affondi</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2364,6 +2496,27 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2290,6 +2290,234 @@
       <c r="B59" t="inlineStr">
         <is>
           <t>affondi</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>stretching</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>plank</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>legraise</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>oblique</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>shoulderpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ropepushdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>benchdips</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>affondi</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>latpulldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>curls</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>plank</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>legraise</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>oblique</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>stretching</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>shoulderpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>benchdips</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2517,6 +2745,55 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -2637,7 +2637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2794,6 +2794,13 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2518,6 +2518,54 @@
       <c r="B78" t="inlineStr">
         <is>
           <t>benchdips</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>latpulldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>affondi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>curls</t>
         </is>
       </c>
     </row>

--- a/GYMapp/gains.xlsx
+++ b/GYMapp/gains.xlsx
@@ -1582,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2566,6 +2566,90 @@
       <c r="B82" t="inlineStr">
         <is>
           <t>curls</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>chestpress45</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>fly</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>shoulderpress</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ropepushdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>latpulldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>curls</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>squat</t>
         </is>
       </c>
     </row>
